--- a/data/trans_bre/P1419-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1419-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,98</t>
+          <t>0,5; 2,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,91</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>1,39</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>122,29%</t>
+          <t>270,04%</t>
         </is>
       </c>
     </row>
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,87</t>
+          <t>2,01; 5,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 2,02</t>
+          <t>-0,12; 1,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 1,43</t>
+          <t>-0,18; 1,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,05</t>
+          <t>0,05; 2,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,93; 1249,75</t>
+          <t>65,56; 907,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,05; 1420,65</t>
+          <t>-43,89; 1230,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-78,04; —</t>
+          <t>-40,45; —</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,05</t>
+          <t>4,19</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>196,04%</t>
+          <t>197,82%</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,81</t>
+          <t>3,49; 7,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 6,92</t>
+          <t>2,65; 6,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,95</t>
+          <t>0,66; 2,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 6,02</t>
+          <t>2,07; 6,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>150,05; 822,54</t>
+          <t>130,92; 807,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>122,14; 2307,38</t>
+          <t>102,47; 2440,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49,08; 515,66</t>
+          <t>60,27; 485,07</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,55</t>
+          <t>8,71</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>367,99%</t>
+          <t>236,85%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 10,0</t>
+          <t>3,44; 9,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,69; 7,4</t>
+          <t>2,66; 7,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 5,36</t>
+          <t>0,92; 5,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 12,32</t>
+          <t>6,17; 10,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>63,95; 375,99</t>
+          <t>59,59; 390,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,61; 870,26</t>
+          <t>79,13; 825,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,05; 264,2</t>
+          <t>21,19; 271,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>169,62; 941,37</t>
+          <t>121,95; 434,57</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,48</t>
+          <t>6,69</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,83; 13,97</t>
+          <t>5,24; 13,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,88; 15,77</t>
+          <t>8,78; 15,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 10,52</t>
+          <t>4,38; 10,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,6; 9,41</t>
+          <t>3,81; 9,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>77,52; 334,95</t>
+          <t>65,78; 327,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>382,17; 3184,42</t>
+          <t>363,92; 2916,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>114,07; 837,48</t>
+          <t>116,27; 936,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>38,47; 166,26</t>
+          <t>43,54; 176,51</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,39</t>
+          <t>9,72</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>161,66%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,92; 20,92</t>
+          <t>10,6; 20,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,69; 17,28</t>
+          <t>8,32; 16,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,28; 15,9</t>
+          <t>7,26; 15,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 10,87</t>
+          <t>6,31; 12,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>108,77; 448,26</t>
+          <t>111,8; 485,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>183,5; 1164,04</t>
+          <t>162,45; 1027,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>142,27; 806,92</t>
+          <t>136,89; 921,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-36,12; 206,5</t>
+          <t>84,12; 287,87</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14,8</t>
+          <t>14,84</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>168,93%</t>
+          <t>166,94%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,55; 22,72</t>
+          <t>9,56; 23,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,24; 26,96</t>
+          <t>16,54; 26,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,78; 16,19</t>
+          <t>6,65; 16,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,67; 18,54</t>
+          <t>10,74; 18,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>72,25; 378,42</t>
+          <t>73,14; 377,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>324,49; 1877,55</t>
+          <t>296,89; 1890,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,89; 650,55</t>
+          <t>93,11; 628,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>93,53; 281,15</t>
+          <t>93,94; 273,78</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,49</t>
+          <t>7,06</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>184,25%</t>
+          <t>184,27%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,67; 9,01</t>
+          <t>6,55; 9,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,28; 8,35</t>
+          <t>6,23; 8,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,69; 5,66</t>
+          <t>3,68; 5,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,63; 7,74</t>
+          <t>6,07; 8,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>192,27; 355,19</t>
+          <t>181,26; 357,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>415,34; 925,64</t>
+          <t>411,1; 927,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>193,28; 453,77</t>
+          <t>197,03; 452,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>125,75; 266,53</t>
+          <t>140,01; 235,56</t>
         </is>
       </c>
     </row>
